--- a/salidas/empresas/AAPL.xlsx
+++ b/salidas/empresas/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>2.258476257324219</v>
+        <v>2.258476734161377</v>
       </c>
       <c r="C2" t="n">
         <v>2.696785926818848</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>2.048509836196899</v>
+        <v>2.048510551452637</v>
       </c>
       <c r="C3" t="n">
         <v>2.446070909500122</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>2.105339050292969</v>
+        <v>2.105339527130127</v>
       </c>
       <c r="C5" t="n">
         <v>2.513928890228271</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>1.78769862651825</v>
+        <v>1.787698745727539</v>
       </c>
       <c r="C6" t="n">
         <v>2.134643077850342</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>1.712924361228943</v>
+        <v>1.712924122810364</v>
       </c>
       <c r="C7" t="n">
         <v>2.04535698890686</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>2.032658338546753</v>
+        <v>2.03265905380249</v>
       </c>
       <c r="C8" t="n">
         <v>2.427143096923828</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>2.02936840057373</v>
+        <v>2.029368162155151</v>
       </c>
       <c r="C9" t="n">
         <v>2.423213958740234</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>2.302444696426392</v>
+        <v>2.302443265914917</v>
       </c>
       <c r="C10" t="n">
         <v>2.749285936355591</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>2.741515636444092</v>
+        <v>2.741516590118408</v>
       </c>
       <c r="C12" t="n">
         <v>3.273571014404297</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>2.537533760070801</v>
+        <v>2.537532806396484</v>
       </c>
       <c r="C13" t="n">
         <v>3.029999971389771</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>2.56415319442749</v>
+        <v>2.564153432846069</v>
       </c>
       <c r="C14" t="n">
         <v>3.061785936355591</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.530654191970825</v>
+        <v>2.530652761459351</v>
       </c>
       <c r="C15" t="n">
         <v>3.021785974502563</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>2.984982013702393</v>
+        <v>2.984980821609497</v>
       </c>
       <c r="C17" t="n">
         <v>3.56428599357605</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>3.624748468399048</v>
+        <v>3.624748945236206</v>
       </c>
       <c r="C18" t="n">
         <v>4.328214168548584</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>3.650171041488647</v>
+        <v>3.650170803070068</v>
       </c>
       <c r="C19" t="n">
         <v>4.35857105255127</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>3.940892696380615</v>
+        <v>3.940893173217773</v>
       </c>
       <c r="C20" t="n">
         <v>4.705714225769043</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>4.141884326934814</v>
+        <v>4.141884803771973</v>
       </c>
       <c r="C21" t="n">
         <v>4.945713996887207</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>4.590231418609619</v>
+        <v>4.590232372283936</v>
       </c>
       <c r="C22" t="n">
         <v>5.481070995330811</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>5.681335926055908</v>
+        <v>5.681333541870117</v>
       </c>
       <c r="C23" t="n">
         <v>6.783928871154785</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>5.450133800506592</v>
+        <v>5.450131416320801</v>
       </c>
       <c r="C24" t="n">
         <v>6.507856845855713</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.924498081207275</v>
+        <v>5.924500942230225</v>
       </c>
       <c r="C25" t="n">
         <v>7.074285984039307</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>4.048568725585938</v>
+        <v>4.048567771911621</v>
       </c>
       <c r="C26" t="n">
         <v>4.834286212921143</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>3.739302635192871</v>
+        <v>3.73930287361145</v>
       </c>
       <c r="C27" t="n">
         <v>4.465000152587891</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>4.292033195495605</v>
+        <v>4.292031764984131</v>
       </c>
       <c r="C28" t="n">
         <v>5.125</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>5.202780246734619</v>
+        <v>5.202779293060303</v>
       </c>
       <c r="C29" t="n">
         <v>6.212500095367432</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>5.64544153213501</v>
+        <v>5.645442962646484</v>
       </c>
       <c r="C30" t="n">
         <v>6.741071224212646</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.008069515228271</v>
+        <v>5.008068561553955</v>
       </c>
       <c r="C31" t="n">
         <v>5.980000019073486</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>4.754136562347412</v>
+        <v>4.754135131835938</v>
       </c>
       <c r="C32" t="n">
         <v>5.676785945892334</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>3.399529457092285</v>
+        <v>3.39952826499939</v>
       </c>
       <c r="C34" t="n">
         <v>4.059286117553711</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>3.217976570129395</v>
+        <v>3.217977285385132</v>
       </c>
       <c r="C35" t="n">
         <v>3.842499971389771</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>2.771725654602051</v>
+        <v>2.771725177764893</v>
       </c>
       <c r="C36" t="n">
         <v>3.309643030166626</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.552787065505981</v>
+        <v>2.552786588668823</v>
       </c>
       <c r="C37" t="n">
         <v>3.048213958740234</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>2.695754528045654</v>
+        <v>2.69575572013855</v>
       </c>
       <c r="C38" t="n">
         <v>3.218929052352905</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>2.671229839324951</v>
+        <v>2.671229362487793</v>
       </c>
       <c r="C39" t="n">
         <v>3.189642906188965</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>3.144100189208984</v>
+        <v>3.144101142883301</v>
       </c>
       <c r="C40" t="n">
         <v>3.754286050796509</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>3.763528347015381</v>
+        <v>3.763527870178223</v>
       </c>
       <c r="C41" t="n">
         <v>4.493928909301758</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>4.062027454376221</v>
+        <v>4.062025547027588</v>
       </c>
       <c r="C42" t="n">
         <v>4.850357055664062</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>4.886935234069824</v>
+        <v>4.88693380355835</v>
       </c>
       <c r="C44" t="n">
         <v>5.835357189178467</v>
@@ -1305,7 +1317,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>5.543751239776611</v>
+        <v>5.543752193450928</v>
       </c>
       <c r="C46" t="n">
         <v>6.619643211364746</v>
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>5.979236125946045</v>
+        <v>5.979235172271729</v>
       </c>
       <c r="C48" t="n">
         <v>7.13964319229126</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>6.3028564453125</v>
+        <v>6.302856922149658</v>
       </c>
       <c r="C49" t="n">
         <v>7.526071071624756</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>5.744443893432617</v>
+        <v>5.744443416595459</v>
       </c>
       <c r="C50" t="n">
         <v>6.859285831451416</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>6.120108127593994</v>
+        <v>6.120107173919678</v>
       </c>
       <c r="C51" t="n">
         <v>7.307857036590576</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>7.028764247894287</v>
+        <v>7.028761386871338</v>
       </c>
       <c r="C52" t="n">
         <v>8.392856597900391</v>
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.683187484741211</v>
+        <v>7.683185577392578</v>
       </c>
       <c r="C54" t="n">
         <v>9.174285888671875</v>
@@ -1555,7 +1567,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>7.694251537322998</v>
+        <v>7.694252967834473</v>
       </c>
       <c r="C56" t="n">
         <v>9.1875</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>7.271030426025391</v>
+        <v>7.271033763885498</v>
       </c>
       <c r="C57" t="n">
         <v>8.682143211364746</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>8.486859321594238</v>
+        <v>8.486855506896973</v>
       </c>
       <c r="C58" t="n">
         <v>10.13392925262451</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>9.002201080322266</v>
+        <v>9.002200126647949</v>
       </c>
       <c r="C59" t="n">
         <v>10.74928569793701</v>
@@ -1684,11 +1696,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.30638313293457</v>
+        <v>9.306381225585938</v>
       </c>
       <c r="C60" t="n">
         <v>11.11250019073486</v>
@@ -1713,7 +1725,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1742,11 +1754,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>10.14893627166748</v>
+        <v>10.14893817901611</v>
       </c>
       <c r="C62" t="n">
         <v>12.11857128143311</v>
@@ -1771,11 +1783,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>10.56438159942627</v>
+        <v>10.56438064575195</v>
       </c>
       <c r="C63" t="n">
         <v>12.61464309692383</v>
@@ -1800,11 +1812,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.42380428314209</v>
+        <v>10.4238109588623</v>
       </c>
       <c r="C64" t="n">
         <v>12.44678592681885</v>
@@ -1829,7 +1841,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1858,11 +1870,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.40346717834473</v>
+        <v>10.40346813201904</v>
       </c>
       <c r="C66" t="n">
         <v>12.42249965667725</v>
@@ -1887,11 +1899,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.03976249694824</v>
+        <v>10.03976821899414</v>
       </c>
       <c r="C67" t="n">
         <v>11.98821353912354</v>
@@ -1916,11 +1928,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>11.67911052703857</v>
+        <v>11.67911434173584</v>
       </c>
       <c r="C68" t="n">
         <v>13.94571399688721</v>
@@ -1945,11 +1957,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>11.51012706756592</v>
+        <v>11.51012802124023</v>
       </c>
       <c r="C69" t="n">
         <v>13.74392890930176</v>
@@ -1974,11 +1986,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>11.40513610839844</v>
+        <v>11.40514183044434</v>
       </c>
       <c r="C70" t="n">
         <v>13.61857128143311</v>
@@ -2003,11 +2015,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.10682010650635</v>
+        <v>12.10682392120361</v>
       </c>
       <c r="C71" t="n">
         <v>14.45642852783203</v>
@@ -2032,11 +2044,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>11.43146133422852</v>
+        <v>11.43146228790283</v>
       </c>
       <c r="C72" t="n">
         <v>13.64999961853027</v>
@@ -2061,11 +2073,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>12.1133975982666</v>
+        <v>12.11339950561523</v>
       </c>
       <c r="C73" t="n">
         <v>14.4642858505249</v>
@@ -2090,11 +2102,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.65314674377441</v>
+        <v>13.65314197540283</v>
       </c>
       <c r="C74" t="n">
         <v>16.3028564453125</v>
@@ -2119,11 +2131,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>16.22417259216309</v>
+        <v>16.22417068481445</v>
       </c>
       <c r="C75" t="n">
         <v>19.37285614013672</v>
@@ -2148,7 +2160,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2177,11 +2189,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>17.46662330627441</v>
+        <v>17.46662902832031</v>
       </c>
       <c r="C77" t="n">
         <v>20.8564281463623</v>
@@ -2206,11 +2218,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>17.27969932556152</v>
+        <v>17.27969551086426</v>
       </c>
       <c r="C78" t="n">
         <v>20.63321495056152</v>
@@ -2235,11 +2247,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.46722984313965</v>
+        <v>17.46721649169922</v>
       </c>
       <c r="C79" t="n">
         <v>20.85714340209961</v>
@@ -2264,11 +2276,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.26761245727539</v>
+        <v>18.26760864257812</v>
       </c>
       <c r="C80" t="n">
         <v>21.81285667419434</v>
@@ -2293,7 +2305,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2322,11 +2334,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>20.03837776184082</v>
+        <v>20.03838157653809</v>
       </c>
       <c r="C82" t="n">
         <v>23.82500076293945</v>
@@ -2351,11 +2363,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.88224601745605</v>
+        <v>17.88225173950195</v>
       </c>
       <c r="C83" t="n">
         <v>21.26142883300781</v>
@@ -2380,11 +2392,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>17.66096687316895</v>
+        <v>17.66096115112305</v>
       </c>
       <c r="C84" t="n">
         <v>20.90285682678223</v>
@@ -2409,11 +2421,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>16.05835723876953</v>
+        <v>16.05836296081543</v>
       </c>
       <c r="C85" t="n">
         <v>19.00607109069824</v>
@@ -2438,11 +2450,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>13.74452209472656</v>
+        <v>13.74452114105225</v>
       </c>
       <c r="C86" t="n">
         <v>16.26749992370605</v>
@@ -2467,11 +2479,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>13.39697742462158</v>
+        <v>13.39697933197021</v>
       </c>
       <c r="C87" t="n">
         <v>15.76428604125977</v>
@@ -2496,11 +2508,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>13.43521881103516</v>
+        <v>13.43522071838379</v>
       </c>
       <c r="C88" t="n">
         <v>15.80928611755371</v>
@@ -2525,11 +2537,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>13.43886375427246</v>
+        <v>13.43886470794678</v>
       </c>
       <c r="C89" t="n">
         <v>15.81357097625732</v>
@@ -2554,11 +2566,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>13.74015617370605</v>
+        <v>13.74015331268311</v>
       </c>
       <c r="C90" t="n">
         <v>16.06178665161133</v>
@@ -2583,11 +2595,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>12.11478805541992</v>
+        <v>12.11478424072266</v>
       </c>
       <c r="C91" t="n">
         <v>14.16178607940674</v>
@@ -2612,11 +2624,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>13.82569980621338</v>
+        <v>13.82569694519043</v>
       </c>
       <c r="C92" t="n">
         <v>16.16178512573242</v>
@@ -2641,11 +2653,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.9838342666626</v>
+        <v>14.98383140563965</v>
       </c>
       <c r="C93" t="n">
         <v>17.40071487426758</v>
@@ -2670,11 +2682,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>14.66184616088867</v>
+        <v>14.66184520721436</v>
       </c>
       <c r="C94" t="n">
         <v>17.02678680419922</v>
@@ -2699,7 +2711,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2728,11 +2740,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>17.20107841491699</v>
+        <v>17.20107460021973</v>
       </c>
       <c r="C96" t="n">
         <v>19.85964393615723</v>
@@ -2757,11 +2769,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>17.35418510437012</v>
+        <v>17.35419273376465</v>
       </c>
       <c r="C97" t="n">
         <v>20.03642845153809</v>
@@ -2786,11 +2798,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>15.48520660400391</v>
+        <v>15.48520183563232</v>
       </c>
       <c r="C98" t="n">
         <v>17.87857055664062</v>
@@ -2815,11 +2827,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>16.37577056884766</v>
+        <v>16.37576675415039</v>
       </c>
       <c r="C99" t="n">
         <v>18.79428672790527</v>
@@ -2844,11 +2856,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>16.70251274108887</v>
+        <v>16.70252227783203</v>
       </c>
       <c r="C100" t="n">
         <v>19.16928672790527</v>
@@ -2873,11 +2885,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>18.36267852783203</v>
+        <v>18.36268424987793</v>
       </c>
       <c r="C101" t="n">
         <v>21.07464218139648</v>
@@ -2902,11 +2914,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>19.8080005645752</v>
+        <v>19.8079948425293</v>
       </c>
       <c r="C102" t="n">
         <v>22.60714340209961</v>
@@ -2931,11 +2943,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>20.35591888427734</v>
+        <v>20.35592842102051</v>
       </c>
       <c r="C103" t="n">
         <v>23.23250007629395</v>
@@ -2960,11 +2972,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>20.94077110290527</v>
+        <v>20.94077491760254</v>
       </c>
       <c r="C104" t="n">
         <v>23.89999961853027</v>
@@ -2989,11 +3001,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>22.56387138366699</v>
+        <v>22.56386947631836</v>
       </c>
       <c r="C105" t="n">
         <v>25.625</v>
@@ -3018,11 +3030,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>22.17864036560059</v>
+        <v>22.17863082885742</v>
       </c>
       <c r="C106" t="n">
         <v>25.1875</v>
@@ -3047,11 +3059,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>23.77462005615234</v>
+        <v>23.77460670471191</v>
       </c>
       <c r="C107" t="n">
         <v>27</v>
@@ -3076,7 +3088,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3105,11 +3117,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>24.40389633178711</v>
+        <v>24.40390396118164</v>
       </c>
       <c r="C109" t="n">
         <v>27.59499931335449</v>
@@ -3134,7 +3146,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3163,11 +3175,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>28.5132999420166</v>
+        <v>28.51329803466797</v>
       </c>
       <c r="C111" t="n">
         <v>32.1150016784668</v>
@@ -3192,11 +3204,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>27.61878776550293</v>
+        <v>27.61878204345703</v>
       </c>
       <c r="C112" t="n">
         <v>31.10750007629395</v>
@@ -3221,11 +3233,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.77859306335449</v>
+        <v>27.77860260009766</v>
       </c>
       <c r="C113" t="n">
         <v>31.28750038146973</v>
@@ -3250,11 +3262,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>29.03806114196777</v>
+        <v>29.03805923461914</v>
       </c>
       <c r="C114" t="n">
         <v>32.56999969482422</v>
@@ -3279,7 +3291,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3308,11 +3320,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>27.0365047454834</v>
+        <v>27.03650093078613</v>
       </c>
       <c r="C116" t="n">
         <v>30.32500076293945</v>
@@ -3337,11 +3349,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>25.24679565429688</v>
+        <v>25.24679183959961</v>
       </c>
       <c r="C117" t="n">
         <v>28.19000053405762</v>
@@ -3366,11 +3378,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>24.69600296020508</v>
+        <v>24.69600868225098</v>
       </c>
       <c r="C118" t="n">
         <v>27.57500076293945</v>
@@ -3395,11 +3407,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>26.7558765411377</v>
+        <v>26.7558708190918</v>
       </c>
       <c r="C119" t="n">
         <v>29.875</v>
@@ -3424,7 +3436,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3453,7 +3465,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3482,11 +3494,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>21.88756370544434</v>
+        <v>21.88756942749023</v>
       </c>
       <c r="C122" t="n">
         <v>24.33499908447266</v>
@@ -3511,11 +3523,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>21.85938835144043</v>
+        <v>21.85938453674316</v>
       </c>
       <c r="C123" t="n">
         <v>24.17250061035156</v>
@@ -3540,11 +3552,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>24.64013290405273</v>
+        <v>24.64013481140137</v>
       </c>
       <c r="C124" t="n">
         <v>27.24749946594238</v>
@@ -3569,11 +3581,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>21.19245529174805</v>
+        <v>21.19245910644531</v>
       </c>
       <c r="C125" t="n">
         <v>23.43499946594238</v>
@@ -3598,11 +3610,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>22.71350288391113</v>
+        <v>22.71350860595703</v>
       </c>
       <c r="C126" t="n">
         <v>24.96500015258789</v>
@@ -3627,7 +3639,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3656,11 +3668,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>23.70292282104492</v>
+        <v>23.70293045043945</v>
       </c>
       <c r="C128" t="n">
         <v>26.05249977111816</v>
@@ -3685,11 +3697,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>24.26354598999023</v>
+        <v>24.26354789733887</v>
       </c>
       <c r="C129" t="n">
         <v>26.52499961853027</v>
@@ -3714,7 +3726,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3743,11 +3755,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>25.96497344970703</v>
+        <v>25.96496963500977</v>
       </c>
       <c r="C131" t="n">
         <v>28.38500022888184</v>
@@ -3772,7 +3784,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3801,11 +3813,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.62235069274902</v>
+        <v>26.62235260009766</v>
       </c>
       <c r="C133" t="n">
         <v>28.95499992370605</v>
@@ -3830,11 +3842,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>27.89348411560059</v>
+        <v>27.89347267150879</v>
       </c>
       <c r="C134" t="n">
         <v>30.33749961853027</v>
@@ -3859,11 +3871,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>31.62500762939453</v>
+        <v>31.62500953674316</v>
       </c>
       <c r="C135" t="n">
         <v>34.24750137329102</v>
@@ -3888,11 +3900,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>33.16482162475586</v>
+        <v>33.16482925415039</v>
       </c>
       <c r="C136" t="n">
         <v>35.91500091552734</v>
@@ -3917,11 +3929,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.16251373291016</v>
+        <v>33.16250228881836</v>
       </c>
       <c r="C137" t="n">
         <v>35.91249847412109</v>
@@ -3946,11 +3958,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>35.41117858886719</v>
+        <v>35.41117095947266</v>
       </c>
       <c r="C138" t="n">
         <v>38.18999862670898</v>
@@ -3975,7 +3987,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -4004,11 +4016,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>34.47698593139648</v>
+        <v>34.47698211669922</v>
       </c>
       <c r="C140" t="n">
         <v>37.18249893188477</v>
@@ -4033,11 +4045,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>38.1660041809082</v>
+        <v>38.16600799560547</v>
       </c>
       <c r="C141" t="n">
         <v>41</v>
@@ -4062,11 +4074,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>35.86672592163086</v>
+        <v>35.86673355102539</v>
       </c>
       <c r="C142" t="n">
         <v>38.52999877929688</v>
@@ -4091,11 +4103,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>39.33891296386719</v>
+        <v>39.33890151977539</v>
       </c>
       <c r="C143" t="n">
         <v>42.2599983215332</v>
@@ -4120,11 +4132,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>40.13662719726562</v>
+        <v>40.13661956787109</v>
       </c>
       <c r="C144" t="n">
         <v>42.96250152587891</v>
@@ -4149,7 +4161,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4178,11 +4190,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>39.10429763793945</v>
+        <v>39.10430526733398</v>
       </c>
       <c r="C146" t="n">
         <v>41.85749816894531</v>
@@ -4207,11 +4219,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>41.7706298828125</v>
+        <v>41.77062225341797</v>
       </c>
       <c r="C147" t="n">
         <v>44.52999877929688</v>
@@ -4236,7 +4248,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4265,11 +4277,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>38.75484466552734</v>
+        <v>38.75485229492188</v>
       </c>
       <c r="C149" t="n">
         <v>41.31499862670898</v>
@@ -4294,11 +4306,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>43.9915657043457</v>
+        <v>43.99156951904297</v>
       </c>
       <c r="C150" t="n">
         <v>46.71749877929688</v>
@@ -4323,11 +4335,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>43.57723236083984</v>
+        <v>43.57721710205078</v>
       </c>
       <c r="C151" t="n">
         <v>46.27750015258789</v>
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4381,11 +4393,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>53.77490997314453</v>
+        <v>53.77492141723633</v>
       </c>
       <c r="C153" t="n">
         <v>56.90750122070312</v>
@@ -4410,7 +4422,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4439,7 +4451,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4468,11 +4480,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>42.33462142944336</v>
+        <v>42.33463287353516</v>
       </c>
       <c r="C156" t="n">
         <v>44.64500045776367</v>
@@ -4497,11 +4509,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>37.39424514770508</v>
+        <v>37.39424133300781</v>
       </c>
       <c r="C157" t="n">
         <v>39.43500137329102</v>
@@ -4526,11 +4538,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>39.45669555664062</v>
+        <v>39.45669174194336</v>
       </c>
       <c r="C158" t="n">
         <v>41.61000061035156</v>
@@ -4555,11 +4567,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>41.22342300415039</v>
+        <v>41.22342681884766</v>
       </c>
       <c r="C159" t="n">
         <v>43.28749847412109</v>
@@ -4584,11 +4596,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>45.22315979003906</v>
+        <v>45.2231559753418</v>
       </c>
       <c r="C160" t="n">
         <v>47.48749923706055</v>
@@ -4613,11 +4625,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>47.77536773681641</v>
+        <v>47.77535629272461</v>
       </c>
       <c r="C161" t="n">
         <v>50.16749954223633</v>
@@ -4642,11 +4654,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>41.84105682373047</v>
+        <v>41.84106063842773</v>
       </c>
       <c r="C162" t="n">
         <v>43.76750183105469</v>
@@ -4671,11 +4683,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>47.3021125793457</v>
+        <v>47.30210876464844</v>
       </c>
       <c r="C163" t="n">
         <v>49.47999954223633</v>
@@ -4700,11 +4712,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>50.91573715209961</v>
+        <v>50.91572189331055</v>
       </c>
       <c r="C164" t="n">
         <v>53.2599983215332</v>
@@ -4729,11 +4741,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>50.07759857177734</v>
+        <v>50.07759094238281</v>
       </c>
       <c r="C165" t="n">
         <v>52.18500137329102</v>
@@ -4758,11 +4770,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>53.7313346862793</v>
+        <v>53.73133087158203</v>
       </c>
       <c r="C166" t="n">
         <v>55.99250030517578</v>
@@ -4787,11 +4799,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>59.67855834960938</v>
+        <v>59.67855072021484</v>
       </c>
       <c r="C167" t="n">
         <v>62.18999862670898</v>
@@ -4816,11 +4828,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>64.30687713623047</v>
+        <v>64.30685424804688</v>
       </c>
       <c r="C168" t="n">
         <v>66.8125</v>
@@ -4845,11 +4857,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>70.65936279296875</v>
+        <v>70.65935516357422</v>
       </c>
       <c r="C169" t="n">
         <v>73.41249847412109</v>
@@ -4874,11 +4886,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>74.47566223144531</v>
+        <v>74.47567749023438</v>
       </c>
       <c r="C170" t="n">
         <v>77.37750244140625</v>
@@ -4903,11 +4915,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>65.93321228027344</v>
+        <v>65.93318939208984</v>
       </c>
       <c r="C171" t="n">
         <v>68.33999633789062</v>
@@ -4932,11 +4944,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>61.3336067199707</v>
+        <v>61.33359909057617</v>
       </c>
       <c r="C172" t="n">
         <v>63.5724983215332</v>
@@ -4961,11 +4973,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>70.86322784423828</v>
+        <v>70.86321258544922</v>
       </c>
       <c r="C173" t="n">
         <v>73.44999694824219</v>
@@ -4990,11 +5002,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>76.89324951171875</v>
+        <v>76.89328002929688</v>
       </c>
       <c r="C174" t="n">
         <v>79.48500061035156</v>
@@ -5019,11 +5031,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>88.22628784179688</v>
+        <v>88.22629547119141</v>
       </c>
       <c r="C175" t="n">
         <v>91.19999694824219</v>
@@ -5048,11 +5060,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>102.7952423095703</v>
+        <v>102.7952346801758</v>
       </c>
       <c r="C176" t="n">
         <v>106.2600021362305</v>
@@ -5077,11 +5089,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>125.0575180053711</v>
+        <v>125.0575485229492</v>
       </c>
       <c r="C177" t="n">
         <v>129.0399932861328</v>
@@ -5106,11 +5118,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>112.2358474731445</v>
+        <v>112.2358551025391</v>
       </c>
       <c r="C178" t="n">
         <v>115.8099975585938</v>
@@ -5135,11 +5147,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>105.5003433227539</v>
+        <v>105.5003509521484</v>
       </c>
       <c r="C179" t="n">
         <v>108.8600006103516</v>
@@ -5164,11 +5176,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>115.5749282836914</v>
+        <v>115.5749053955078</v>
       </c>
       <c r="C180" t="n">
         <v>119.0500030517578</v>
@@ -5193,11 +5205,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>128.8167572021484</v>
+        <v>128.8167419433594</v>
       </c>
       <c r="C181" t="n">
         <v>132.6900024414062</v>
@@ -5222,7 +5234,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5251,11 +5263,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>117.8963165283203</v>
+        <v>117.8963088989258</v>
       </c>
       <c r="C183" t="n">
         <v>121.2600021362305</v>
@@ -5280,7 +5292,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5309,7 +5321,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5338,11 +5350,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>121.3591766357422</v>
+        <v>121.3591690063477</v>
       </c>
       <c r="C186" t="n">
         <v>124.6100006103516</v>
@@ -5367,7 +5379,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5396,7 +5408,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5425,11 +5437,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>148.0905609130859</v>
+        <v>148.0906066894531</v>
       </c>
       <c r="C189" t="n">
         <v>151.8300018310547</v>
@@ -5454,11 +5466,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>138.0150299072266</v>
+        <v>138.0149993896484</v>
       </c>
       <c r="C190" t="n">
         <v>141.5</v>
@@ -5483,11 +5495,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>146.1106109619141</v>
+        <v>146.110595703125</v>
       </c>
       <c r="C191" t="n">
         <v>149.8000030517578</v>
@@ -5512,11 +5524,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>161.4641571044922</v>
+        <v>161.464111328125</v>
       </c>
       <c r="C192" t="n">
         <v>165.3000030517578</v>
@@ -5541,11 +5553,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>173.4494171142578</v>
+        <v>173.4494323730469</v>
       </c>
       <c r="C193" t="n">
         <v>177.5700073242188</v>
@@ -5570,7 +5582,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5599,11 +5611,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>161.4938201904297</v>
+        <v>161.4938049316406</v>
       </c>
       <c r="C195" t="n">
         <v>165.1199951171875</v>
@@ -5628,11 +5640,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>170.7754211425781</v>
+        <v>170.775390625</v>
       </c>
       <c r="C196" t="n">
         <v>174.6100006103516</v>
@@ -5657,7 +5669,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5686,11 +5698,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>145.7852478027344</v>
+        <v>145.7852325439453</v>
       </c>
       <c r="C198" t="n">
         <v>148.8399963378906</v>
@@ -5715,11 +5727,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>133.9139556884766</v>
+        <v>133.9140014648438</v>
       </c>
       <c r="C199" t="n">
         <v>136.7200012207031</v>
@@ -5744,7 +5756,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5773,11 +5785,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>154.2071838378906</v>
+        <v>154.2071228027344</v>
       </c>
       <c r="C201" t="n">
         <v>157.2200012207031</v>
@@ -5802,11 +5814,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>135.5516052246094</v>
+        <v>135.5515899658203</v>
       </c>
       <c r="C202" t="n">
         <v>138.1999969482422</v>
@@ -5831,11 +5843,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>150.4014587402344</v>
+        <v>150.4014739990234</v>
       </c>
       <c r="C203" t="n">
         <v>153.3399963378906</v>
@@ -5860,11 +5872,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>145.4340972900391</v>
+        <v>145.4341278076172</v>
       </c>
       <c r="C204" t="n">
         <v>148.0299987792969</v>
@@ -5889,11 +5901,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>127.651481628418</v>
+        <v>127.6514892578125</v>
       </c>
       <c r="C205" t="n">
         <v>129.9299926757812</v>
@@ -5918,7 +5930,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5947,11 +5959,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>145.0460968017578</v>
+        <v>145.0461120605469</v>
       </c>
       <c r="C207" t="n">
         <v>147.4100036621094</v>
@@ -5976,11 +5988,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>162.2556457519531</v>
+        <v>162.2556304931641</v>
       </c>
       <c r="C208" t="n">
         <v>164.8999938964844</v>
@@ -6005,11 +6017,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>166.9589996337891</v>
+        <v>166.9589691162109</v>
       </c>
       <c r="C209" t="n">
         <v>169.6799926757812</v>
@@ -6034,11 +6046,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>174.6488647460938</v>
+        <v>174.6488189697266</v>
       </c>
       <c r="C210" t="n">
         <v>177.25</v>
@@ -6063,11 +6075,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>191.1234283447266</v>
+        <v>191.1234588623047</v>
       </c>
       <c r="C211" t="n">
         <v>193.9700012207031</v>
@@ -6092,7 +6104,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6121,11 +6133,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>185.3629455566406</v>
+        <v>185.3629150390625</v>
       </c>
       <c r="C213" t="n">
         <v>187.8699951171875</v>
@@ -6150,11 +6162,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>168.9252777099609</v>
+        <v>168.9252624511719</v>
       </c>
       <c r="C214" t="n">
         <v>171.2100067138672</v>
@@ -6179,7 +6191,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6208,11 +6220,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>187.6620941162109</v>
+        <v>187.6621246337891</v>
       </c>
       <c r="C216" t="n">
         <v>189.9499969482422</v>
@@ -6237,11 +6249,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>190.2110137939453</v>
+        <v>190.2110290527344</v>
       </c>
       <c r="C217" t="n">
         <v>192.5299987792969</v>
@@ -6266,11 +6278,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>182.1789245605469</v>
+        <v>182.178955078125</v>
       </c>
       <c r="C218" t="n">
         <v>184.3999938964844</v>
@@ -6295,11 +6307,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>178.80078125</v>
+        <v>178.8007659912109</v>
       </c>
       <c r="C219" t="n">
         <v>180.75</v>
@@ -6324,11 +6336,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>169.6307373046875</v>
+        <v>169.6307220458984</v>
       </c>
       <c r="C220" t="n">
         <v>171.4799957275391</v>
@@ -6353,11 +6365,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>168.4931488037109</v>
+        <v>168.4931640625</v>
       </c>
       <c r="C221" t="n">
         <v>170.3300018310547</v>
@@ -6382,11 +6394,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>190.4346923828125</v>
+        <v>190.4347076416016</v>
       </c>
       <c r="C222" t="n">
         <v>192.25</v>
@@ -6411,11 +6423,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>208.6312255859375</v>
+        <v>208.6312408447266</v>
       </c>
       <c r="C223" t="n">
         <v>210.6199951171875</v>
@@ -6440,7 +6452,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6469,11 +6481,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>227.1002807617188</v>
+        <v>227.1002655029297</v>
       </c>
       <c r="C225" t="n">
         <v>229</v>
@@ -6498,11 +6510,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>231.0670928955078</v>
+        <v>231.0670776367188</v>
       </c>
       <c r="C226" t="n">
         <v>233</v>
@@ -6527,11 +6539,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>224.035888671875</v>
+        <v>224.0359039306641</v>
       </c>
       <c r="C227" t="n">
         <v>225.9100036621094</v>
@@ -6556,11 +6568,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>235.6201019287109</v>
+        <v>235.6201171875</v>
       </c>
       <c r="C228" t="n">
         <v>237.3300018310547</v>
@@ -6585,11 +6597,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>248.6157836914062</v>
+        <v>248.6157989501953</v>
       </c>
       <c r="C229" t="n">
         <v>250.4199981689453</v>
@@ -6614,11 +6626,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>234.2996826171875</v>
+        <v>234.2996673583984</v>
       </c>
       <c r="C230" t="n">
         <v>236</v>
@@ -6643,11 +6655,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>240.3615875244141</v>
+        <v>240.3616180419922</v>
       </c>
       <c r="C231" t="n">
         <v>241.8399963378906</v>
@@ -6672,11 +6684,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>220.7720947265625</v>
+        <v>220.7721099853516</v>
       </c>
       <c r="C232" t="n">
         <v>222.1300048828125</v>
@@ -6701,11 +6713,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>211.2009735107422</v>
+        <v>211.200927734375</v>
       </c>
       <c r="C233" t="n">
         <v>212.5</v>
@@ -6730,7 +6742,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6759,11 +6771,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>204.1831665039062</v>
+        <v>204.1831512451172</v>
       </c>
       <c r="C235" t="n">
         <v>205.1699981689453</v>
@@ -6788,11 +6800,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>206.5716094970703</v>
+        <v>206.5716247558594</v>
       </c>
       <c r="C236" t="n">
         <v>207.5700073242188</v>
@@ -6817,7 +6829,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6846,7 +6858,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6875,7 +6887,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6904,7 +6916,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6933,7 +6945,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6962,7 +6974,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6991,7 +7003,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7020,7 +7032,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7049,7 +7061,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7107,7 +7119,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7136,7 +7148,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7165,7 +7177,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7194,32 +7206,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="C250" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="D250" t="n">
-        <v>723207900</v>
+        <v>747965300</v>
       </c>
       <c r="E250" t="n">
         <v>8.709999999999999</v>
       </c>
       <c r="F250" t="n">
-        <v>38.6934545365869</v>
+        <v>38.56716572075022</v>
       </c>
       <c r="G250" t="n">
         <v>14594180000</v>
       </c>
       <c r="H250" t="n">
-        <v>4918530383263.55</v>
+        <v>4902477141566.772</v>
       </c>
       <c r="I250" t="n">
-        <v>0.04955454160494115</v>
+        <v>0.05125093016531247</v>
       </c>
     </row>
   </sheetData>
@@ -7251,75 +7263,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39537</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39627</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7355,13 +7367,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39719</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39809</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40203</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7397,13 +7409,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39810</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39900</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7439,13 +7451,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39901</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39991</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7481,13 +7493,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40082</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7514,7 +7526,7 @@
       <c r="I6" t="n">
         <v>0.3003571428571429</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="K6" t="n">
@@ -7527,13 +7539,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40083</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40173</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40203</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7560,7 +7572,7 @@
       <c r="I7" t="n">
         <v>0.3421428571428571</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="K7" t="n">
@@ -7573,13 +7585,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40174</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40264</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7606,7 +7618,7 @@
       <c r="I8" t="n">
         <v>0.3971428571428571</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="K8" t="n">
@@ -7619,13 +7631,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40265</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40355</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40380</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7652,7 +7664,7 @@
       <c r="I9" t="n">
         <v>0.4742857142857143</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="K9" t="n">
@@ -7665,13 +7677,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40356</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40446</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7698,7 +7710,7 @@
       <c r="I10" t="n">
         <v>0.5410714285714285</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="K10" t="n">
@@ -7711,13 +7723,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40447</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40537</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40562</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7744,7 +7756,7 @@
       <c r="I11" t="n">
         <v>0.6396428571428571</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40562</v>
       </c>
       <c r="K11" t="n">
@@ -7757,13 +7769,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40538</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40628</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7790,7 +7802,7 @@
       <c r="I12" t="n">
         <v>0.7492857142857143</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="K12" t="n">
@@ -7803,13 +7815,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40629</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40719</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7836,7 +7848,7 @@
       <c r="I13" t="n">
         <v>0.902142857142857</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="K13" t="n">
@@ -7849,13 +7861,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40720</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40810</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7882,7 +7894,7 @@
       <c r="I14" t="n">
         <v>0.9882142857142857</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K14" t="n">
@@ -7895,13 +7907,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40811</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40933</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7928,7 +7940,7 @@
       <c r="I15" t="n">
         <v>1.253928571428571</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40933</v>
       </c>
       <c r="K15" t="n">
@@ -7941,13 +7953,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7974,7 +7986,7 @@
       <c r="I16" t="n">
         <v>1.464642857142857</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="K16" t="n">
@@ -7987,13 +7999,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8020,7 +8032,7 @@
       <c r="I17" t="n">
         <v>1.519285714285714</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K17" t="n">
@@ -8033,13 +8045,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8066,7 +8078,7 @@
       <c r="I18" t="n">
         <v>1.577142857142857</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="K18" t="n">
@@ -8079,13 +8091,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41272</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41298</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8112,7 +8124,7 @@
       <c r="I19" t="n">
         <v>1.575</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41298</v>
       </c>
       <c r="K19" t="n">
@@ -8125,13 +8137,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8158,7 +8170,7 @@
       <c r="I20" t="n">
         <v>1.496071428571428</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K20" t="n">
@@ -8171,13 +8183,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8204,7 +8216,7 @@
       <c r="I21" t="n">
         <v>1.43</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K21" t="n">
@@ -8217,13 +8229,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8250,7 +8262,7 @@
       <c r="I22" t="n">
         <v>1.415357142857143</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K22" t="n">
@@ -8263,13 +8275,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41636</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8296,7 +8308,7 @@
       <c r="I23" t="n">
         <v>1.44</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="K23" t="n">
@@ -8309,13 +8321,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8342,7 +8354,7 @@
       <c r="I24" t="n">
         <v>1.494642857142857</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K24" t="n">
@@ -8355,13 +8367,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8388,7 +8400,7 @@
       <c r="I25" t="n">
         <v>1.547857142857143</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K25" t="n">
@@ -8401,13 +8413,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8434,7 +8446,7 @@
       <c r="I26" t="n">
         <v>1.607857142857143</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="K26" t="n">
@@ -8447,13 +8459,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42000</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42032</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8480,7 +8492,7 @@
       <c r="I27" t="n">
         <v>1.855</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42032</v>
       </c>
       <c r="K27" t="n">
@@ -8493,13 +8505,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42091</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8526,7 +8538,7 @@
       <c r="I28" t="n">
         <v>2.0225</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="K28" t="n">
@@ -8539,13 +8551,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42182</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8572,7 +8584,7 @@
       <c r="I29" t="n">
         <v>2.165</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="K29" t="n">
@@ -8585,13 +8597,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42273</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8618,7 +8630,7 @@
       <c r="I30" t="n">
         <v>2.3</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="K30" t="n">
@@ -8631,13 +8643,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42364</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8664,7 +8676,7 @@
       <c r="I31" t="n">
         <v>2.355</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="K31" t="n">
@@ -8677,13 +8689,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42365</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42455</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8710,7 +8722,7 @@
       <c r="I32" t="n">
         <v>2.2475</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K32" t="n">
@@ -8723,13 +8735,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42456</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42546</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8756,7 +8768,7 @@
       <c r="I33" t="n">
         <v>2.14</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K33" t="n">
@@ -8769,13 +8781,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42547</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42637</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8802,7 +8814,7 @@
       <c r="I34" t="n">
         <v>2.0675</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K34" t="n">
@@ -8815,13 +8827,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42638</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8848,7 +8860,7 @@
       <c r="I35" t="n">
         <v>2.0875</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="K35" t="n">
@@ -8861,13 +8873,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8894,7 +8906,7 @@
       <c r="I36" t="n">
         <v>2.1375</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8907,13 +8919,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8940,7 +8952,7 @@
       <c r="I37" t="n">
         <v>2.2</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K37" t="n">
@@ -8953,13 +8965,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8986,7 +8998,7 @@
       <c r="I38" t="n">
         <v>2.3</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K38" t="n">
@@ -8999,13 +9011,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43099</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9032,7 +9044,7 @@
       <c r="I39" t="n">
         <v>2.4325</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="K39" t="n">
@@ -9045,13 +9057,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9078,7 +9090,7 @@
       <c r="I40" t="n">
         <v>2.59</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9091,13 +9103,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9124,7 +9136,7 @@
       <c r="I41" t="n">
         <v>2.7575</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K41" t="n">
@@ -9137,13 +9149,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9170,7 +9182,7 @@
       <c r="I42" t="n">
         <v>2.9675</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K42" t="n">
@@ -9183,13 +9195,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43463</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9216,7 +9228,7 @@
       <c r="I43" t="n">
         <v>3.04</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="K43" t="n">
@@ -9229,13 +9241,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9262,7 +9274,7 @@
       <c r="I44" t="n">
         <v>2.9725</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K44" t="n">
@@ -9275,13 +9287,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9308,7 +9320,7 @@
       <c r="I45" t="n">
         <v>2.9325</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K45" t="n">
@@ -9321,13 +9333,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9354,7 +9366,7 @@
       <c r="I46" t="n">
         <v>2.962499999999999</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K46" t="n">
@@ -9367,13 +9379,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43827</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9400,7 +9412,7 @@
       <c r="I47" t="n">
         <v>3.165</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="K47" t="n">
@@ -9413,13 +9425,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43918</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9446,7 +9458,7 @@
       <c r="I48" t="n">
         <v>3.1875</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K48" t="n">
@@ -9459,13 +9471,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44009</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9492,7 +9504,7 @@
       <c r="I49" t="n">
         <v>3.2875</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K49" t="n">
@@ -9505,13 +9517,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44100</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9538,7 +9550,7 @@
       <c r="I50" t="n">
         <v>3.26</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K50" t="n">
@@ -9551,13 +9563,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44191</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9584,7 +9596,7 @@
       <c r="I51" t="n">
         <v>3.6925</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="K51" t="n">
@@ -9597,13 +9609,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44282</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9630,7 +9642,7 @@
       <c r="I52" t="n">
         <v>4.454999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9643,13 +9655,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44373</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9676,7 +9688,7 @@
       <c r="I53" t="n">
         <v>5.109999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K53" t="n">
@@ -9689,13 +9701,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44374</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44464</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9722,7 +9734,7 @@
       <c r="I54" t="n">
         <v>5.609999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K54" t="n">
@@ -9735,13 +9747,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44465</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44555</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9768,7 +9780,7 @@
       <c r="I55" t="n">
         <v>6.03</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="K55" t="n">
@@ -9781,13 +9793,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44556</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44646</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9814,7 +9826,7 @@
       <c r="I56" t="n">
         <v>6.15</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K56" t="n">
@@ -9827,13 +9839,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44647</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44737</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9860,7 +9872,7 @@
       <c r="I57" t="n">
         <v>6.05</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K57" t="n">
@@ -9873,13 +9885,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44738</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44828</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9906,7 +9918,7 @@
       <c r="I58" t="n">
         <v>6.109999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K58" t="n">
@@ -9919,13 +9931,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44829</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9952,7 +9964,7 @@
       <c r="I59" t="n">
         <v>5.89</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="K59" t="n">
@@ -9965,13 +9977,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9998,7 +10010,7 @@
       <c r="I60" t="n">
         <v>5.89</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K60" t="n">
@@ -10011,13 +10023,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10044,7 +10056,7 @@
       <c r="I61" t="n">
         <v>5.95</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10057,13 +10069,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10090,7 +10102,7 @@
       <c r="I62" t="n">
         <v>6.13</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K62" t="n">
@@ -10103,13 +10115,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10136,7 +10148,7 @@
       <c r="I63" t="n">
         <v>6.43</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="K63" t="n">
@@ -10149,13 +10161,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10182,7 +10194,7 @@
       <c r="I64" t="n">
         <v>6.44</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K64" t="n">
@@ -10195,13 +10207,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10228,7 +10240,7 @@
       <c r="I65" t="n">
         <v>6.58</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K65" t="n">
@@ -10241,13 +10253,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10274,7 +10286,7 @@
       <c r="I66" t="n">
         <v>6.080000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K66" t="n">
@@ -10287,13 +10299,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10320,7 +10332,7 @@
       <c r="I67" t="n">
         <v>6.300000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K67" t="n">
@@ -10333,13 +10345,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10366,7 +10378,7 @@
       <c r="I68" t="n">
         <v>6.42</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K68" t="n">
@@ -10379,13 +10391,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10412,7 +10424,7 @@
       <c r="I69" t="n">
         <v>6.590000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K69" t="n">
@@ -10425,13 +10437,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10458,7 +10470,7 @@
       <c r="I70" t="n">
         <v>7.46</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K70" t="n">
@@ -10471,13 +10483,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46018</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10504,7 +10516,7 @@
       <c r="I71" t="n">
         <v>7.899999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K71" t="n">
@@ -10517,13 +10529,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10550,7 +10562,7 @@
       <c r="I72" t="n">
         <v>8.26</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K72" t="n">
@@ -10563,13 +10575,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46200</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10596,7 +10608,7 @@
       <c r="I73" t="n">
         <v>8.709999999999999</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K73" t="n">
@@ -10633,52 +10645,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39991</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="C2" t="n">
@@ -10707,10 +10719,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="C3" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40193</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40203</v>
       </c>
       <c r="C4" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40277</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="C5" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40368</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40380</v>
       </c>
       <c r="C6" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="C7" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40550</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40562</v>
       </c>
       <c r="C8" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40641</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="C9" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40732</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="C10" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40830</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C11" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40921</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40933</v>
       </c>
       <c r="C12" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41012</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="C13" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41103</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C14" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41201</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C15" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41285</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41298</v>
       </c>
       <c r="C16" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41376</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="C17" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41467</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C18" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C19" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41649</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="C20" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41740</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C21" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41831</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C22" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41922</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="C23" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42013</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42032</v>
       </c>
       <c r="C24" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42104</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C25" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42195</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="C26" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42286</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C27" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42377</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="C28" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42468</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C29" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42657</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C31" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42755</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="C32" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C35" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43119</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="C36" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C38" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C39" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43483</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="C40" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43577</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C43" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43847</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="C44" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43938</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C47" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44211</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="C48" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44484</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C51" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44575</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="C52" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44666</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44757</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C54" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44848</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44946</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="C56" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C57" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C58" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C59" t="n">
@@ -12531,10 +12543,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45310</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="C60" t="n">
@@ -12563,10 +12575,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C61" t="n">
@@ -12595,10 +12607,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C62" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C63" t="n">
@@ -12659,10 +12671,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45674</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C64" t="n">
@@ -12691,10 +12703,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45765</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C65" t="n">
@@ -12723,10 +12735,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12755,10 +12767,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C67" t="n">
@@ -12787,10 +12799,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46038</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C68" t="n">
@@ -12819,10 +12831,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12851,10 +12863,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C70" t="n">
@@ -12901,12 +12913,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/AAPL.xlsx
+++ b/salidas/empresas/AAPL.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>2.258476734161377</v>
+        <v>2.258476495742798</v>
       </c>
       <c r="C2" t="n">
         <v>2.696785926818848</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>2.048510551452637</v>
+        <v>2.048510074615479</v>
       </c>
       <c r="C3" t="n">
         <v>2.446070909500122</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>1.875932097434998</v>
+        <v>1.875932335853577</v>
       </c>
       <c r="C4" t="n">
         <v>2.240000009536743</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>2.105339527130127</v>
+        <v>2.105340003967285</v>
       </c>
       <c r="C5" t="n">
         <v>2.513928890228271</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>1.712924122810364</v>
+        <v>1.712924361228943</v>
       </c>
       <c r="C7" t="n">
         <v>2.04535698890686</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>2.03265905380249</v>
+        <v>2.032658815383911</v>
       </c>
       <c r="C8" t="n">
         <v>2.427143096923828</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>2.302443265914917</v>
+        <v>2.302443504333496</v>
       </c>
       <c r="C10" t="n">
         <v>2.749285936355591</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>2.425072431564331</v>
+        <v>2.42507266998291</v>
       </c>
       <c r="C11" t="n">
         <v>2.895714044570923</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>2.741516590118408</v>
+        <v>2.74151611328125</v>
       </c>
       <c r="C12" t="n">
         <v>3.273571014404297</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>2.537532806396484</v>
+        <v>2.537532329559326</v>
       </c>
       <c r="C13" t="n">
         <v>3.029999971389771</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>2.564153432846069</v>
+        <v>2.564152240753174</v>
       </c>
       <c r="C14" t="n">
         <v>3.061785936355591</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.530652761459351</v>
+        <v>2.530653476715088</v>
       </c>
       <c r="C15" t="n">
         <v>3.021785974502563</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>2.984980821609497</v>
+        <v>2.984981298446655</v>
       </c>
       <c r="C17" t="n">
         <v>3.56428599357605</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>3.624748945236206</v>
+        <v>3.62474799156189</v>
       </c>
       <c r="C18" t="n">
         <v>4.328214168548584</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>3.650170803070068</v>
+        <v>3.650171518325806</v>
       </c>
       <c r="C19" t="n">
         <v>4.35857105255127</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>3.940893173217773</v>
+        <v>3.940891742706299</v>
       </c>
       <c r="C20" t="n">
         <v>4.705714225769043</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>4.141884803771973</v>
+        <v>4.141885757446289</v>
       </c>
       <c r="C21" t="n">
         <v>4.945713996887207</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>4.590232372283936</v>
+        <v>4.590230941772461</v>
       </c>
       <c r="C22" t="n">
         <v>5.481070995330811</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>5.681333541870117</v>
+        <v>5.681334972381592</v>
       </c>
       <c r="C23" t="n">
         <v>6.783928871154785</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>5.450131416320801</v>
+        <v>5.450132369995117</v>
       </c>
       <c r="C24" t="n">
         <v>6.507856845855713</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.924500942230225</v>
+        <v>5.924499988555908</v>
       </c>
       <c r="C25" t="n">
         <v>7.074285984039307</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>4.048567771911621</v>
+        <v>4.048569202423096</v>
       </c>
       <c r="C26" t="n">
         <v>4.834286212921143</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>3.73930287361145</v>
+        <v>3.739302158355713</v>
       </c>
       <c r="C27" t="n">
         <v>4.465000152587891</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>5.202779293060303</v>
+        <v>5.202780723571777</v>
       </c>
       <c r="C29" t="n">
         <v>6.212500095367432</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>5.645442962646484</v>
+        <v>5.645443439483643</v>
       </c>
       <c r="C30" t="n">
         <v>6.741071224212646</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.008068561553955</v>
+        <v>5.00806999206543</v>
       </c>
       <c r="C31" t="n">
         <v>5.980000019073486</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>4.754135131835938</v>
+        <v>4.754134654998779</v>
       </c>
       <c r="C32" t="n">
         <v>5.676785945892334</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>3.39952826499939</v>
+        <v>3.399528026580811</v>
       </c>
       <c r="C34" t="n">
         <v>4.059286117553711</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>3.217977285385132</v>
+        <v>3.217977046966553</v>
       </c>
       <c r="C35" t="n">
         <v>3.842499971389771</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>2.771725177764893</v>
+        <v>2.77172589302063</v>
       </c>
       <c r="C36" t="n">
         <v>3.309643030166626</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.552786588668823</v>
+        <v>2.552786350250244</v>
       </c>
       <c r="C37" t="n">
         <v>3.048213958740234</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>2.69575572013855</v>
+        <v>2.695755481719971</v>
       </c>
       <c r="C38" t="n">
         <v>3.218929052352905</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>2.671229362487793</v>
+        <v>2.671229600906372</v>
       </c>
       <c r="C39" t="n">
         <v>3.189642906188965</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>3.763527870178223</v>
+        <v>3.763529539108276</v>
       </c>
       <c r="C41" t="n">
         <v>4.493928909301758</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>4.062025547027588</v>
+        <v>4.062026500701904</v>
       </c>
       <c r="C42" t="n">
         <v>4.850357055664062</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>4.260029792785645</v>
+        <v>4.260027408599854</v>
       </c>
       <c r="C43" t="n">
         <v>5.086785793304443</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>4.88693380355835</v>
+        <v>4.886935234069824</v>
       </c>
       <c r="C44" t="n">
         <v>5.835357189178467</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>5.031099319458008</v>
+        <v>5.031097888946533</v>
       </c>
       <c r="C45" t="n">
         <v>6.007500171661377</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>5.543752193450928</v>
+        <v>5.543749809265137</v>
       </c>
       <c r="C46" t="n">
         <v>6.619643211364746</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>5.637965679168701</v>
+        <v>5.637965202331543</v>
       </c>
       <c r="C47" t="n">
         <v>6.732142925262451</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>5.979235172271729</v>
+        <v>5.979237079620361</v>
       </c>
       <c r="C48" t="n">
         <v>7.13964319229126</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>6.302856922149658</v>
+        <v>6.302855968475342</v>
       </c>
       <c r="C49" t="n">
         <v>7.526071071624756</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>5.744443416595459</v>
+        <v>5.744443893432617</v>
       </c>
       <c r="C50" t="n">
         <v>6.859285831451416</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>6.120107173919678</v>
+        <v>6.120109081268311</v>
       </c>
       <c r="C51" t="n">
         <v>7.307857036590576</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>7.028761386871338</v>
+        <v>7.028763771057129</v>
       </c>
       <c r="C52" t="n">
         <v>8.392856597900391</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>7.809103012084961</v>
+        <v>7.809108257293701</v>
       </c>
       <c r="C53" t="n">
         <v>9.324643135070801</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>7.52316951751709</v>
+        <v>7.523168563842773</v>
       </c>
       <c r="C55" t="n">
         <v>8.983214378356934</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>7.694252967834473</v>
+        <v>7.694250106811523</v>
       </c>
       <c r="C56" t="n">
         <v>9.1875</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>7.271033763885498</v>
+        <v>7.271030426025391</v>
       </c>
       <c r="C57" t="n">
         <v>8.682143211364746</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>9.002200126647949</v>
+        <v>9.002201080322266</v>
       </c>
       <c r="C59" t="n">
         <v>10.74928569793701</v>
@@ -1700,7 +1700,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.306381225585938</v>
+        <v>9.306379318237305</v>
       </c>
       <c r="C60" t="n">
         <v>11.11250019073486</v>
@@ -1758,7 +1758,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>10.14893817901611</v>
+        <v>10.14893436431885</v>
       </c>
       <c r="C62" t="n">
         <v>12.11857128143311</v>
@@ -1816,7 +1816,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.4238109588623</v>
+        <v>10.42380809783936</v>
       </c>
       <c r="C64" t="n">
         <v>12.44678592681885</v>
@@ -1845,7 +1845,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>10.47226047515869</v>
+        <v>10.47226142883301</v>
       </c>
       <c r="C65" t="n">
         <v>12.50464344024658</v>
@@ -1874,7 +1874,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.40346813201904</v>
+        <v>10.40346717834473</v>
       </c>
       <c r="C66" t="n">
         <v>12.42249965667725</v>
@@ -1932,7 +1932,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>11.67911434173584</v>
+        <v>11.67911052703857</v>
       </c>
       <c r="C68" t="n">
         <v>13.94571399688721</v>
@@ -1961,7 +1961,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>11.51012802124023</v>
+        <v>11.51012229919434</v>
       </c>
       <c r="C69" t="n">
         <v>13.74392890930176</v>
@@ -1990,7 +1990,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>11.40514183044434</v>
+        <v>11.40514087677002</v>
       </c>
       <c r="C70" t="n">
         <v>13.61857128143311</v>
@@ -2019,7 +2019,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.10682392120361</v>
+        <v>12.10681915283203</v>
       </c>
       <c r="C71" t="n">
         <v>14.45642852783203</v>
@@ -2048,7 +2048,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>11.43146228790283</v>
+        <v>11.43146133422852</v>
       </c>
       <c r="C72" t="n">
         <v>13.64999961853027</v>
@@ -2106,7 +2106,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.65314197540283</v>
+        <v>13.65314865112305</v>
       </c>
       <c r="C74" t="n">
         <v>16.3028564453125</v>
@@ -2135,7 +2135,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>16.22417068481445</v>
+        <v>16.22417640686035</v>
       </c>
       <c r="C75" t="n">
         <v>19.37285614013672</v>
@@ -2164,7 +2164,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>17.93231964111328</v>
+        <v>17.93232154846191</v>
       </c>
       <c r="C76" t="n">
         <v>21.41250038146973</v>
@@ -2193,7 +2193,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>17.46662902832031</v>
+        <v>17.46662521362305</v>
       </c>
       <c r="C77" t="n">
         <v>20.8564281463623</v>
@@ -2222,7 +2222,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>17.27969551086426</v>
+        <v>17.27968215942383</v>
       </c>
       <c r="C78" t="n">
         <v>20.63321495056152</v>
@@ -2251,7 +2251,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.46721649169922</v>
+        <v>17.46722602844238</v>
       </c>
       <c r="C79" t="n">
         <v>20.85714340209961</v>
@@ -2280,7 +2280,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.26760864257812</v>
+        <v>18.26761627197266</v>
       </c>
       <c r="C80" t="n">
         <v>21.81285667419434</v>
@@ -2338,7 +2338,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>20.03838157653809</v>
+        <v>20.03838539123535</v>
       </c>
       <c r="C82" t="n">
         <v>23.82500076293945</v>
@@ -2367,7 +2367,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.88225173950195</v>
+        <v>17.88224029541016</v>
       </c>
       <c r="C83" t="n">
         <v>21.26142883300781</v>
@@ -2396,7 +2396,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>17.66096115112305</v>
+        <v>17.66096305847168</v>
       </c>
       <c r="C84" t="n">
         <v>20.90285682678223</v>
@@ -2454,7 +2454,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>13.74452114105225</v>
+        <v>13.74452018737793</v>
       </c>
       <c r="C86" t="n">
         <v>16.26749992370605</v>
@@ -2512,7 +2512,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>13.43522071838379</v>
+        <v>13.43521976470947</v>
       </c>
       <c r="C88" t="n">
         <v>15.80928611755371</v>
@@ -2541,7 +2541,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>13.43886470794678</v>
+        <v>13.43886375427246</v>
       </c>
       <c r="C89" t="n">
         <v>15.81357097625732</v>
@@ -2570,7 +2570,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>13.74015331268311</v>
+        <v>13.74015712738037</v>
       </c>
       <c r="C90" t="n">
         <v>16.06178665161133</v>
@@ -2599,7 +2599,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>12.11478424072266</v>
+        <v>12.11479091644287</v>
       </c>
       <c r="C91" t="n">
         <v>14.16178607940674</v>
@@ -2628,7 +2628,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>13.82569694519043</v>
+        <v>13.82569885253906</v>
       </c>
       <c r="C92" t="n">
         <v>16.16178512573242</v>
@@ -2657,7 +2657,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.98383140563965</v>
+        <v>14.98383331298828</v>
       </c>
       <c r="C93" t="n">
         <v>17.40071487426758</v>
@@ -2686,7 +2686,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>14.66184520721436</v>
+        <v>14.6618480682373</v>
       </c>
       <c r="C94" t="n">
         <v>17.02678680419922</v>
@@ -2715,7 +2715,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>16.07497596740723</v>
+        <v>16.07497787475586</v>
       </c>
       <c r="C95" t="n">
         <v>18.66785621643066</v>
@@ -2744,7 +2744,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>17.20107460021973</v>
+        <v>17.20107078552246</v>
       </c>
       <c r="C96" t="n">
         <v>19.85964393615723</v>
@@ -2773,7 +2773,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>17.35419273376465</v>
+        <v>17.35419082641602</v>
       </c>
       <c r="C97" t="n">
         <v>20.03642845153809</v>
@@ -2802,7 +2802,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>15.48520183563232</v>
+        <v>15.48520088195801</v>
       </c>
       <c r="C98" t="n">
         <v>17.87857055664062</v>
@@ -2831,7 +2831,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>16.37576675415039</v>
+        <v>16.37576866149902</v>
       </c>
       <c r="C99" t="n">
         <v>18.79428672790527</v>
@@ -2860,7 +2860,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>16.70252227783203</v>
+        <v>16.70251655578613</v>
       </c>
       <c r="C100" t="n">
         <v>19.16928672790527</v>
@@ -2889,7 +2889,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>18.36268424987793</v>
+        <v>18.36268043518066</v>
       </c>
       <c r="C101" t="n">
         <v>21.07464218139648</v>
@@ -2918,7 +2918,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>19.8079948425293</v>
+        <v>19.80799674987793</v>
       </c>
       <c r="C102" t="n">
         <v>22.60714340209961</v>
@@ -2947,7 +2947,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>20.35592842102051</v>
+        <v>20.35592651367188</v>
       </c>
       <c r="C103" t="n">
         <v>23.23250007629395</v>
@@ -2976,7 +2976,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>20.94077491760254</v>
+        <v>20.94077682495117</v>
       </c>
       <c r="C104" t="n">
         <v>23.89999961853027</v>
@@ -3005,7 +3005,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>22.56386947631836</v>
+        <v>22.56386756896973</v>
       </c>
       <c r="C105" t="n">
         <v>25.625</v>
@@ -3034,7 +3034,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>22.17863082885742</v>
+        <v>22.17863655090332</v>
       </c>
       <c r="C106" t="n">
         <v>25.1875</v>
@@ -3063,7 +3063,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>23.77460670471191</v>
+        <v>23.77462196350098</v>
       </c>
       <c r="C107" t="n">
         <v>27</v>
@@ -3092,7 +3092,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>26.29421615600586</v>
+        <v>26.29421997070312</v>
       </c>
       <c r="C108" t="n">
         <v>29.73250007629395</v>
@@ -3121,7 +3121,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>24.40390396118164</v>
+        <v>24.40390014648438</v>
       </c>
       <c r="C109" t="n">
         <v>27.59499931335449</v>
@@ -3179,7 +3179,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>28.51329803466797</v>
+        <v>28.5132942199707</v>
       </c>
       <c r="C111" t="n">
         <v>32.1150016784668</v>
@@ -3208,7 +3208,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>27.61878204345703</v>
+        <v>27.61878967285156</v>
       </c>
       <c r="C112" t="n">
         <v>31.10750007629395</v>
@@ -3237,7 +3237,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.77860260009766</v>
+        <v>27.77859687805176</v>
       </c>
       <c r="C113" t="n">
         <v>31.28750038146973</v>
@@ -3266,7 +3266,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>29.03805923461914</v>
+        <v>29.03805351257324</v>
       </c>
       <c r="C114" t="n">
         <v>32.56999969482422</v>
@@ -3295,7 +3295,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>27.9570426940918</v>
+        <v>27.95703887939453</v>
       </c>
       <c r="C115" t="n">
         <v>31.35750007629395</v>
@@ -3324,7 +3324,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>27.03650093078613</v>
+        <v>27.03650856018066</v>
       </c>
       <c r="C116" t="n">
         <v>30.32500076293945</v>
@@ -3353,7 +3353,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>25.24679183959961</v>
+        <v>25.24679756164551</v>
       </c>
       <c r="C117" t="n">
         <v>28.19000053405762</v>
@@ -3411,7 +3411,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>26.7558708190918</v>
+        <v>26.75586700439453</v>
       </c>
       <c r="C119" t="n">
         <v>29.875</v>
@@ -3440,7 +3440,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>26.60057258605957</v>
+        <v>26.6005744934082</v>
       </c>
       <c r="C120" t="n">
         <v>29.57500076293945</v>
@@ -3469,7 +3469,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>23.6684398651123</v>
+        <v>23.66843223571777</v>
       </c>
       <c r="C121" t="n">
         <v>26.31500053405762</v>
@@ -3498,7 +3498,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>21.88756942749023</v>
+        <v>21.88757133483887</v>
       </c>
       <c r="C122" t="n">
         <v>24.33499908447266</v>
@@ -3527,7 +3527,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>21.85938453674316</v>
+        <v>21.85938835144043</v>
       </c>
       <c r="C123" t="n">
         <v>24.17250061035156</v>
@@ -3585,7 +3585,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>21.19245910644531</v>
+        <v>21.19246101379395</v>
       </c>
       <c r="C125" t="n">
         <v>23.43499946594238</v>
@@ -3614,7 +3614,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>22.71350860595703</v>
+        <v>22.71349906921387</v>
       </c>
       <c r="C126" t="n">
         <v>24.96500015258789</v>
@@ -3643,7 +3643,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>21.74454689025879</v>
+        <v>21.74455642700195</v>
       </c>
       <c r="C127" t="n">
         <v>23.89999961853027</v>
@@ -3759,7 +3759,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>25.96496963500977</v>
+        <v>25.96496772766113</v>
       </c>
       <c r="C131" t="n">
         <v>28.38500022888184</v>
@@ -3817,7 +3817,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.62235260009766</v>
+        <v>26.62236022949219</v>
       </c>
       <c r="C133" t="n">
         <v>28.95499992370605</v>
@@ -3846,7 +3846,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>27.89347267150879</v>
+        <v>27.89348411560059</v>
       </c>
       <c r="C134" t="n">
         <v>30.33749961853027</v>
@@ -3904,7 +3904,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>33.16482925415039</v>
+        <v>33.16482162475586</v>
       </c>
       <c r="C136" t="n">
         <v>35.91500091552734</v>
@@ -3933,7 +3933,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.16250228881836</v>
+        <v>33.16251754760742</v>
       </c>
       <c r="C137" t="n">
         <v>35.91249847412109</v>
@@ -3962,7 +3962,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>35.41117095947266</v>
+        <v>35.41117477416992</v>
       </c>
       <c r="C138" t="n">
         <v>38.18999862670898</v>
@@ -3991,7 +3991,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>33.38516235351562</v>
+        <v>33.38516616821289</v>
       </c>
       <c r="C139" t="n">
         <v>36.00500106811523</v>
@@ -4049,7 +4049,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>38.16600799560547</v>
+        <v>38.16599273681641</v>
       </c>
       <c r="C141" t="n">
         <v>41</v>
@@ -4078,7 +4078,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>35.86673355102539</v>
+        <v>35.86674118041992</v>
       </c>
       <c r="C142" t="n">
         <v>38.52999877929688</v>
@@ -4107,7 +4107,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>39.33890151977539</v>
+        <v>39.33889770507812</v>
       </c>
       <c r="C143" t="n">
         <v>42.2599983215332</v>
@@ -4136,7 +4136,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>40.13661956787109</v>
+        <v>40.13662338256836</v>
       </c>
       <c r="C144" t="n">
         <v>42.96250152587891</v>
@@ -4194,7 +4194,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>39.10430526733398</v>
+        <v>39.10429763793945</v>
       </c>
       <c r="C146" t="n">
         <v>41.85749816894531</v>
@@ -4252,7 +4252,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>39.3458137512207</v>
+        <v>39.34580230712891</v>
       </c>
       <c r="C148" t="n">
         <v>41.94499969482422</v>
@@ -4310,7 +4310,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>43.99156951904297</v>
+        <v>43.99156188964844</v>
       </c>
       <c r="C150" t="n">
         <v>46.71749877929688</v>
@@ -4339,7 +4339,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>43.57721710205078</v>
+        <v>43.57723999023438</v>
       </c>
       <c r="C151" t="n">
         <v>46.27750015258789</v>
@@ -4368,7 +4368,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>44.79666900634766</v>
+        <v>44.79668045043945</v>
       </c>
       <c r="C152" t="n">
         <v>47.5724983215332</v>
@@ -4397,7 +4397,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>53.77492141723633</v>
+        <v>53.77491760253906</v>
       </c>
       <c r="C153" t="n">
         <v>56.90750122070312</v>
@@ -4426,7 +4426,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>53.32842636108398</v>
+        <v>53.32842254638672</v>
       </c>
       <c r="C154" t="n">
         <v>56.43500137329102</v>
@@ -4455,7 +4455,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>51.70310592651367</v>
+        <v>51.70312118530273</v>
       </c>
       <c r="C155" t="n">
         <v>54.71500015258789</v>
@@ -4484,7 +4484,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>42.33463287353516</v>
+        <v>42.33462905883789</v>
       </c>
       <c r="C156" t="n">
         <v>44.64500045776367</v>
@@ -4513,7 +4513,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>37.39424133300781</v>
+        <v>37.39424896240234</v>
       </c>
       <c r="C157" t="n">
         <v>39.43500137329102</v>
@@ -4542,7 +4542,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>39.45669174194336</v>
+        <v>39.45669555664062</v>
       </c>
       <c r="C158" t="n">
         <v>41.61000061035156</v>
@@ -4571,7 +4571,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>41.22342681884766</v>
+        <v>41.22342300415039</v>
       </c>
       <c r="C159" t="n">
         <v>43.28749847412109</v>
@@ -4600,7 +4600,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>45.2231559753418</v>
+        <v>45.22314071655273</v>
       </c>
       <c r="C160" t="n">
         <v>47.48749923706055</v>
@@ -4629,7 +4629,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>47.77535629272461</v>
+        <v>47.77536010742188</v>
       </c>
       <c r="C161" t="n">
         <v>50.16749954223633</v>
@@ -4745,7 +4745,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>50.07759094238281</v>
+        <v>50.07759857177734</v>
       </c>
       <c r="C165" t="n">
         <v>52.18500137329102</v>
@@ -4774,7 +4774,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>53.73133087158203</v>
+        <v>53.73132705688477</v>
       </c>
       <c r="C166" t="n">
         <v>55.99250030517578</v>
@@ -4803,7 +4803,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>59.67855072021484</v>
+        <v>59.67855453491211</v>
       </c>
       <c r="C167" t="n">
         <v>62.18999862670898</v>
@@ -4832,7 +4832,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>64.30685424804688</v>
+        <v>64.306884765625</v>
       </c>
       <c r="C168" t="n">
         <v>66.8125</v>
@@ -4919,7 +4919,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>65.93318939208984</v>
+        <v>65.93317413330078</v>
       </c>
       <c r="C171" t="n">
         <v>68.33999633789062</v>
@@ -4948,7 +4948,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>61.33359909057617</v>
+        <v>61.33361434936523</v>
       </c>
       <c r="C172" t="n">
         <v>63.5724983215332</v>
@@ -4977,7 +4977,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>70.86321258544922</v>
+        <v>70.86323547363281</v>
       </c>
       <c r="C173" t="n">
         <v>73.44999694824219</v>
@@ -5035,7 +5035,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>88.22629547119141</v>
+        <v>88.22628784179688</v>
       </c>
       <c r="C175" t="n">
         <v>91.19999694824219</v>
@@ -5064,7 +5064,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>102.7952346801758</v>
+        <v>102.7952423095703</v>
       </c>
       <c r="C176" t="n">
         <v>106.2600021362305</v>
@@ -5093,7 +5093,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>125.0575485229492</v>
+        <v>125.0575561523438</v>
       </c>
       <c r="C177" t="n">
         <v>129.0399932861328</v>
@@ -5122,7 +5122,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>112.2358551025391</v>
+        <v>112.2358474731445</v>
       </c>
       <c r="C178" t="n">
         <v>115.8099975585938</v>
@@ -5151,7 +5151,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>105.5003509521484</v>
+        <v>105.5003433227539</v>
       </c>
       <c r="C179" t="n">
         <v>108.8600006103516</v>
@@ -5180,7 +5180,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>115.5749053955078</v>
+        <v>115.5748977661133</v>
       </c>
       <c r="C180" t="n">
         <v>119.0500030517578</v>
@@ -5209,7 +5209,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>128.8167419433594</v>
+        <v>128.8167572021484</v>
       </c>
       <c r="C181" t="n">
         <v>132.6900024414062</v>
@@ -5267,7 +5267,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>117.8963088989258</v>
+        <v>117.8963165283203</v>
       </c>
       <c r="C183" t="n">
         <v>121.2600021362305</v>
@@ -5296,7 +5296,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>118.7616195678711</v>
+        <v>118.761604309082</v>
       </c>
       <c r="C184" t="n">
         <v>122.1500015258789</v>
@@ -5325,7 +5325,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>127.8133697509766</v>
+        <v>127.8133544921875</v>
       </c>
       <c r="C185" t="n">
         <v>131.4600067138672</v>
@@ -5354,7 +5354,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>121.3591690063477</v>
+        <v>121.3591842651367</v>
       </c>
       <c r="C186" t="n">
         <v>124.6100006103516</v>
@@ -5383,7 +5383,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>133.3870086669922</v>
+        <v>133.3870239257812</v>
       </c>
       <c r="C187" t="n">
         <v>136.9600067138672</v>
@@ -5412,7 +5412,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>142.0548095703125</v>
+        <v>142.0547943115234</v>
       </c>
       <c r="C188" t="n">
         <v>145.8600006103516</v>
@@ -5470,7 +5470,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>138.0149993896484</v>
+        <v>138.0150146484375</v>
       </c>
       <c r="C190" t="n">
         <v>141.5</v>
@@ -5528,7 +5528,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>161.464111328125</v>
+        <v>161.4641418457031</v>
       </c>
       <c r="C192" t="n">
         <v>165.3000030517578</v>
@@ -5557,7 +5557,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>173.4494323730469</v>
+        <v>173.4494476318359</v>
       </c>
       <c r="C193" t="n">
         <v>177.5700073242188</v>
@@ -5615,7 +5615,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>161.4938049316406</v>
+        <v>161.4938201904297</v>
       </c>
       <c r="C195" t="n">
         <v>165.1199951171875</v>
@@ -5644,7 +5644,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>170.775390625</v>
+        <v>170.7754364013672</v>
       </c>
       <c r="C196" t="n">
         <v>174.6100006103516</v>
@@ -5673,7 +5673,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>154.1878662109375</v>
+        <v>154.1878814697266</v>
       </c>
       <c r="C197" t="n">
         <v>157.6499938964844</v>
@@ -5731,7 +5731,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>133.9140014648438</v>
+        <v>133.9139709472656</v>
       </c>
       <c r="C199" t="n">
         <v>136.7200012207031</v>
@@ -5760,7 +5760,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>159.1746368408203</v>
+        <v>159.1746826171875</v>
       </c>
       <c r="C200" t="n">
         <v>162.5099945068359</v>
@@ -5818,7 +5818,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>135.5515899658203</v>
+        <v>135.5516204833984</v>
       </c>
       <c r="C202" t="n">
         <v>138.1999969482422</v>
@@ -5847,7 +5847,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>150.4014739990234</v>
+        <v>150.4014892578125</v>
       </c>
       <c r="C203" t="n">
         <v>153.3399963378906</v>
@@ -5876,7 +5876,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>145.4341278076172</v>
+        <v>145.4341125488281</v>
       </c>
       <c r="C204" t="n">
         <v>148.0299987792969</v>
@@ -5905,7 +5905,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>127.6514892578125</v>
+        <v>127.6515045166016</v>
       </c>
       <c r="C205" t="n">
         <v>129.9299926757812</v>
@@ -5934,7 +5934,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>141.7596893310547</v>
+        <v>141.7596740722656</v>
       </c>
       <c r="C206" t="n">
         <v>144.2899932861328</v>
@@ -5963,7 +5963,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>145.0461120605469</v>
+        <v>145.0461273193359</v>
       </c>
       <c r="C207" t="n">
         <v>147.4100036621094</v>
@@ -5992,7 +5992,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>162.2556304931641</v>
+        <v>162.2555999755859</v>
       </c>
       <c r="C208" t="n">
         <v>164.8999938964844</v>
@@ -6050,7 +6050,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>174.6488189697266</v>
+        <v>174.6488494873047</v>
       </c>
       <c r="C210" t="n">
         <v>177.25</v>
@@ -6079,7 +6079,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>191.1234588623047</v>
+        <v>191.1234436035156</v>
       </c>
       <c r="C211" t="n">
         <v>193.9700012207031</v>
@@ -6137,7 +6137,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>185.3629150390625</v>
+        <v>185.3629302978516</v>
       </c>
       <c r="C213" t="n">
         <v>187.8699951171875</v>
@@ -6195,7 +6195,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>168.4911499023438</v>
+        <v>168.4911193847656</v>
       </c>
       <c r="C215" t="n">
         <v>170.7700042724609</v>
@@ -6224,7 +6224,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>187.6621246337891</v>
+        <v>187.6620941162109</v>
       </c>
       <c r="C216" t="n">
         <v>189.9499969482422</v>
@@ -6253,7 +6253,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>190.2110290527344</v>
+        <v>190.2110137939453</v>
       </c>
       <c r="C217" t="n">
         <v>192.5299987792969</v>
@@ -6311,7 +6311,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>178.8007659912109</v>
+        <v>178.8007965087891</v>
       </c>
       <c r="C219" t="n">
         <v>180.75</v>
@@ -6369,7 +6369,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>168.4931640625</v>
+        <v>168.4931488037109</v>
       </c>
       <c r="C221" t="n">
         <v>170.3300018310547</v>
@@ -6427,7 +6427,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>208.6312408447266</v>
+        <v>208.6312561035156</v>
       </c>
       <c r="C223" t="n">
         <v>210.6199951171875</v>
@@ -6485,7 +6485,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>227.1002655029297</v>
+        <v>227.1002807617188</v>
       </c>
       <c r="C225" t="n">
         <v>229</v>
@@ -6572,7 +6572,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>235.6201171875</v>
+        <v>235.6201019287109</v>
       </c>
       <c r="C228" t="n">
         <v>237.3300018310547</v>
@@ -6601,7 +6601,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>248.6157989501953</v>
+        <v>248.6157836914062</v>
       </c>
       <c r="C229" t="n">
         <v>250.4199981689453</v>
@@ -6630,7 +6630,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>234.2996673583984</v>
+        <v>234.2996826171875</v>
       </c>
       <c r="C230" t="n">
         <v>236</v>
@@ -6659,7 +6659,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>240.3616180419922</v>
+        <v>240.3615875244141</v>
       </c>
       <c r="C231" t="n">
         <v>241.8399963378906</v>
@@ -6688,7 +6688,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>220.7721099853516</v>
+        <v>220.7720794677734</v>
       </c>
       <c r="C232" t="n">
         <v>222.1300048828125</v>
@@ -6717,7 +6717,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>211.200927734375</v>
+        <v>211.2009582519531</v>
       </c>
       <c r="C233" t="n">
         <v>212.5</v>
@@ -6746,7 +6746,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>199.8839416503906</v>
+        <v>199.8839569091797</v>
       </c>
       <c r="C234" t="n">
         <v>200.8500061035156</v>
@@ -6862,7 +6862,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>253.69287109375</v>
+        <v>253.6928863525391</v>
       </c>
       <c r="C238" t="n">
         <v>254.6300048828125</v>
@@ -6978,7 +6978,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>258.775634765625</v>
+        <v>258.7756652832031</v>
       </c>
       <c r="C242" t="n">
         <v>259.4800109863281</v>
@@ -7007,7 +7007,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>263.7094116210938</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="C243" t="n">
         <v>264.1799926757812</v>
@@ -7036,7 +7036,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>253.3379058837891</v>
+        <v>253.337890625</v>
       </c>
       <c r="C244" t="n">
         <v>253.7899932861328</v>
